--- a/veri/ornek/ornek_urunler.xlsx
+++ b/veri/ornek/ornek_urunler.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ürün Kodu</t>
+          <t>StokKodu</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Ürün Adı</t>
+          <t>StokAdi</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,228 +434,226 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Palet İçi Adet</t>
+          <t>Palet içi adet</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Header Kod</t>
+          <t>Kamyon yükleme adeti</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Aksesuar mı</t>
+          <t>Tır yükleme adeti</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KMB-24-ERP</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kombi 24 kW ErP</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kombi</t>
+          <t>KOMBİ</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>234</v>
+      </c>
+      <c r="F2" t="n">
+        <v>468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KMB-28-ERP</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kombi 28 kW ErP</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kombi</t>
+          <t>KOMBİ</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>208</v>
+      </c>
+      <c r="F3" t="n">
+        <v>416</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KMB-BACA</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kombi Baca Seti</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kombi</t>
+          <t>AKSESUAR</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HDR-KMB-24</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
+        <v>77</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1078</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kombi 24 kW (Header)</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kombi</t>
+          <t>PANEL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HDR-KMB-24</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>195</v>
+      </c>
+      <c r="F5" t="n">
+        <v>377</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RAD-600-1000</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Panel Radyatör 600x1000</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Radyatör</t>
+          <t>PANEL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="E6" t="n">
+        <v>330</v>
+      </c>
+      <c r="F6" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Termosifon 80 lt</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Termosifon</t>
+          <t>PANEL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="E7" t="n">
+        <v>390</v>
+      </c>
+      <c r="F7" t="n">
+        <v>754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Klima 12000 BTU</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Klima</t>
+          <t>TERMOSİFON</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="E8" t="n">
+        <v>144</v>
+      </c>
+      <c r="F8" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Isı Pompası 8 kW</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Isı Pompası</t>
+          <t>ISI POMPASI</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32</v>
+      </c>
+      <c r="F9" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
